--- a/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件一.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件一.xlsx
@@ -1,179 +1,580 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="126">
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>台词编号</t>
+  </si>
+  <si>
+    <t>台词/旁白文本</t>
+  </si>
+  <si>
+    <t>立绘/动作提示</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>连续六天的高强度工作，让你的大脑仿佛被塞进了一团生锈的齿轮</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>选题会、改稿、复盘数据……你的生活被切割成无数个以小时为单位的碎片，每一片都填满了别人的情绪，唯独没有你自己的</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>你急需一个出口，一个可以被动的、不消耗自己的放松方式</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>于是你想到了那个正在做的选题，“当代年轻人电竞社交与情感代偿”</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>与其在二手资料里打转，不如亲自下水，把自己变成样本</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>你拿起手机，点开了目前市面上最火的陪玩App</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>首页上铺满了各式各样的陪玩卡片，甜妹、御姐、奶狗、狼狗，标签花里胡哨得像是菜市场里争奇斗艳的招牌</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>你的视线在各种头像和简介上扫过，心里却在评估</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>最终，你的手指停在了“至尊盲盒单”上</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>好评率100%，没有头像，没有简介，没有花里胡哨的标签，只有一串数字</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>——累计服务时长：3472小时，评分：5.0</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>把选择权交给算法，把惊喜留给运气。对于你这种选择困难症来说，简直是救星</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>你点击下单，并在备注栏里飞快地敲下几行要求</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>话少，情绪稳定，不需要刻意讨好，能接得住任何逆风局。</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>订单刚发出，几乎是在同一瞬间，一个纯黑色的默认头像跳进了你的聊天框</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>你戴上降噪耳机，一道极其温润、干净的青年音顺着电流落入耳廓</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>老板晚上好，我是时安。接下来的时间，我会全力配合您的节奏。</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>进入游戏后，作为观察者，你刻意选择了一个极度考验配合、且容错率极低的高爆发输出位</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>你的打法也带着一种强势的压迫感，开局便毫无顾忌地入侵敌方野区，试图探出对方的底线</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>然而，你们的配合却出奇地默契。他没有对你激进的打法提出任何质疑，反而完美地契合了你的每一个意图</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>左侧草丛安全，对方打野在下半区露头了，老板，您可以直接进场，我留了控制技能掩护你。</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>每当你准备冲锋陷阵，耳机里总会适时传来他温和却精准的报点，他总能提前为你扫清视野的盲区，无需多言便能心意相通</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>直到对局进行到二十分钟的关键团战，你为了强切敌方核心，走位出现了致命失误，角色冲进了三个人的包围圈</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>屏幕变成了代表死亡的灰白色，己方阵型随之溃败，高地塔岌岌可危</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>按照常理，这种关键时刻的“送人头”行为，足以让大多数玩家心态爆炸、开麦抱怨</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>但你的耳机里，不仅没有传来预想中的叹气，甚至连一丝情绪波动的杂音都没有</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>安静到你能听见他轻微的呼吸声，然后，他的声音响起</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>我的错，刚才给你的护盾慢了，没保住你。</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>他用最平稳的语气，毫不犹豫地揽下了责任，随后迅速切出计分板复盘，语速飞快地布置下一波止损战术</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>对面双C为了抓你，已经交了全部关键技能和闪现。老板别急，我去清线守高地，你复活后直接带线拿龙，这局能翻，信我。</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>在他的冷静指挥下，你们成功抗住了敌方的一波强推，并在你复活后完成了一波极其漂亮的反打，直接推平了对面的水晶</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>确实有点意思，无论是游戏，还是时安。但比起复盘对局，你对复盘他的表现更感兴趣</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>作为常年剖析人的内容创作者，你敏锐地察觉到，这种极致的情绪控制，绝非单纯的“脾气好”</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>这是一种极高的双商和近乎可怕的自我克制力，他能在关键时刻压抑住自己的情绪反应，用理性替代本能</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>他仿佛一个深不见底的湖泊，能够无声无息地消化掉所有外来的情绪垃圾</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>结算界面弹出，你随手点开打赏界面，刷了一个价值三位数的虚拟礼物这对你来说，是购买高质量研究样本的合理开销</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>屏幕上顿时绽开绚烂的特效，金色的光效在屏幕上炸开，像是一场小型烟花秀</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>耳机那头陷入短暂的沉默，然后，一声极轻的笑声从听筒里传来</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>谢谢老板的打赏，不过您出手这么大方，倒让我觉得……刚才的服务还不够周到，受之有愧了。</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>他的声音里带着一丝不易察觉的窘迫，不是那种“被钱砸晕”的窘迫，而是那种“我做了什么值得这么多”的困惑</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>你靠在椅背上，胜利带来的喜悦让你心情不错</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>你转了一下椅子，目光从屏幕移到窗外的夜色上，连语气也带上一丝棋逢对手的欣赏</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>打得不错，这钱花得很值。你的情绪控制很完美，是个不可多得的优质样本，希望下次还能和你合作。</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>耳机那头又安静了，可能在想怎么回应这句近乎商品评估的夸奖</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>然后他的声音才再次响起，比之前低了几分，像是被你的直白弄得有些措手不及</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>谢谢老板，能成为您的优质样本，是我的荣幸，期待下次为您服务。</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>他的措辞依然专业，语气依然温和，他选择了最安全的方式，顺着你的话，把自己放进你给他划定的框里</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>今晚的样本采集，很成功</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>你将刚才录制的几段高光操作保存进素材库，文件名你打上了“时安_样本001_情绪控制示范”</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>然后你才开口，语气平淡得像是在汇报工作</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>不用有负担，我刚好在做关于虚拟陪伴的社会向选题，今天算是打了个很好的素材。</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>你顿了顿，又补了一句</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>所以这笔打赏，是合理的调研支出，你不用觉得受之有愧。</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>你把所有可能产生暧昧感的缝隙，都用“调研”“支出”这些词填得严严实实</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>这是你的职业习惯，也是你的保护色，把一切私人化的东西，都框定在交易的边界里</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>原来是这样，很高兴能为老板的事业添砖加瓦。您还需要素材的话，随时联系我。</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>添砖加瓦这个词用得很妙，不是帮忙，不是支持，而是一个把自己放在辅助位置的、谦逊又不卑不亢的说法</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>他没有因为被当成工具人而表现出哪怕一丝的抵触，依旧保持着那份无懈可击的专业素养，顺从地接过了你的话茬</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>或许他会是一个值得深入研究的样本</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,156 +874,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +1082,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1338,731 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D60"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="115" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>